--- a/tests/fixtures/21_monthly_budget/pattern.xlsx
+++ b/tests/fixtures/21_monthly_budget/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_income</t>
+          <t>worksheet_title_label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Income:</t>
+          <t>Title of this worksheet is in cell at right. Next instruction is in cell A4.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c_cat</t>
+          <t>worksheet.title</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c_proj</t>
+          <t>col_proj_income_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Projected Monthly Income label is in cell at right. Enter Income 1 in cell E4 and Extra Income in E5 to calculate Total monthly income in E6. Next instruction is in cell A6.</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_act</t>
+          <t>col_proj_income</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>PROJECTED MONTHLY INCOME</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_diff</t>
+          <t>col_income1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,41 +539,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Income 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>budget.income</t>
+          <t>col_income1_value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>4300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item.category</t>
+          <t>col_proj_balance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,29 +583,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>PROJECTED BALANCE \n\(Projected income minus expenses\)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item.projected</t>
+          <t>col_proj_balance_value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>3405</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item.actual</t>
+          <t>proj.income1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item.difference</t>
+          <t>proj.income1_value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -649,92 +649,778 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\$\d+(\.\d{2})?</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>proj.balance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cell:C4</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>budget.income</t>
+          <t>proj.balance_value</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>\$\d+(\.\d{2})?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>table:*</t>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>col_actual_income_label</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Actual Monthly Income label is in cell at right. Enter Income 1 in cell E8 and Extra Income in E9 to calculate Total monthly income in E10. Next instruction is in cell A12.</t>
         </is>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>col_actual_income</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>c_cat</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>c_proj</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>c_act</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>c_diff</t>
+          <t>ACTUAL MONTHLY INCOME</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DATA:*</t>
+          <t>col_actual_income1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>item.category</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>item.projected</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>item.actual</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>item.difference</t>
+          <t>Income 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>col_actual_income1_value</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>col_difference</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DIFFERENCE \n\(Actual minus projected\)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>col_difference_value</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>actual.income1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>actual.income1_value</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>\$\d+(\.\d{2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>col_details_label</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Enter details in Housing table starting in cell at right and in Entertainment table starting in cell G12. Next instruction is in cell A25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>col_housing</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>col_projected_cost</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Projected Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>col_actual_cost</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Actual Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>col_difference_cost</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>col_entertainment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ENTERTAINMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>details.housing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>details.projected_cost</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>\$\d+(\.\d{2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>details.actual_cost</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>\$\d+(\.\d{2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>details.difference_cost</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>\$\d+(\.\d{2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>details.entertainment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>worksheet_title_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>worksheet.title</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>col_proj_income_label</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>col_proj_income</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>col_income1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>col_income1_value</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>col_proj_balance</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>col_proj_balance_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DATA:2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>proj.income1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>proj.income1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>proj.income1_value</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>proj.balance</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>proj.balance_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>col_actual_income_label</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>col_actual_income</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>col_actual_income1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>col_actual_income1_value</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>col_difference</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>col_difference_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DATA:2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>actual.income1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>actual.income1_value</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>col_details_label</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>col_housing</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>col_projected_cost</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>col_actual_cost</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>col_difference_cost</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>col_entertainment</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>col_projected_cost</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>col_actual_cost</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>col_difference_cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DATA:52</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>details.housing</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>details.housing</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>details.projected_cost</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>details.actual_cost</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>details.difference_cost</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>details.entertainment</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>details.projected_cost</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>details.actual_cost</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>details.difference_cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/21_monthly_budget/pattern.xlsx
+++ b/tests/fixtures/21_monthly_budget/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>worksheet_title_label</t>
+          <t>col_proj_cost</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Title of this worksheet is in cell at right. Next instruction is in cell A4.</t>
+          <t>Projected Cost</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>worksheet.title</t>
+          <t>col_actual_cost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>Actual Cost</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>col_proj_income_label</t>
+          <t>col_difference</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,19 +495,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Projected Monthly Income label is in cell at right. Enter Income 1 in cell E4 and Extra Income in E5 to calculate Total monthly income in E6. Next instruction is in cell A6.</t>
+          <t>Difference</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>col_proj_income</t>
+          <t>budget.title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,95 +517,95 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PROJECTED MONTHLY INCOME</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>col_income1</t>
+          <t>income.proj_total</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Income 1</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>col_income1_value</t>
+          <t>income.actual_total</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>col_proj_balance</t>
+          <t>balance.projected</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PROJECTED BALANCE \n\(Projected income minus expenses\)</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>col_proj_balance_value</t>
+          <t>balance.actual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>proj.income1</t>
+          <t>balance.difference</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,17 +639,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>proj.income1_value</t>
+          <t>expense.category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>\$\d+(\.\d{2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>proj.balance</t>
+          <t>expense.projected</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>proj.balance_value</t>
+          <t>expense.actual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -693,734 +693,174 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>\$\d+(\.\d{2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>col_actual_income_label</t>
+          <t>expense.difference</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Actual Monthly Income label is in cell at right. Enter Income 1 in cell E8 and Extra Income in E9 to calculate Total monthly income in E10. Next instruction is in cell A12.</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>col_actual_income</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ACTUAL MONTHLY INCOME</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>cell:B2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>col_actual_income1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Income 1</t>
+          <t>budget.title</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>cell:J4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>col_actual_income1_value</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4000</t>
+          <t>balance.projected</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>cell:E6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>col_difference</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DIFFERENCE \n\(Actual minus projected\)</t>
+          <t>income.proj_total</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>cell:J6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>col_difference_value</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-341</t>
+          <t>balance.actual</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:J8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>actual.income1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>balance.difference</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:E10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>actual.income1_value</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>\$\d+(\.\d{2})?</t>
+          <t>income.actual_total</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>col_details_label</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter details in Housing table starting in cell at right and in Entertainment table starting in cell G12. Next instruction is in cell A25.</t>
+          <t>table:*</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>col_housing</t>
+          <t>HEADER:1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HOUSING</t>
+          <t>col_proj_cost</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>col_actual_cost</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>col_difference</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>col_projected_cost</t>
+          <t>DATA:*</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>expense.category</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Projected Cost</t>
+          <t>expense.projected</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>expense.actual</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>expense.difference</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>col_actual_cost</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Actual Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>col_difference_cost</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>col_entertainment</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ENTERTAINMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>details.housing</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>details.projected_cost</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>\$\d+(\.\d{2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>details.actual_cost</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>\$\d+(\.\d{2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>details.difference_cost</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>\$\d+(\.\d{2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>details.entertainment</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>START:</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>worksheet_title_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>worksheet.title</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>col_proj_income_label</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>col_proj_income</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>col_income1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>col_income1_value</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>col_proj_balance</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>col_proj_balance_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>DATA:2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>proj.income1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>proj.income1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>proj.income1_value</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>proj.balance</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>proj.balance_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>col_actual_income_label</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>col_actual_income</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>col_actual_income1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>col_actual_income1_value</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>col_difference</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>col_difference_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>DATA:2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>actual.income1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>actual.income1_value</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>col_details_label</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>col_housing</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>col_projected_cost</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>col_actual_cost</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>col_difference_cost</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>col_entertainment</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>col_projected_cost</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>col_actual_cost</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>col_difference_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>DATA:52</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>details.housing</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>details.housing</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>details.projected_cost</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>details.actual_cost</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>details.difference_cost</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>details.entertainment</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>details.projected_cost</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>details.actual_cost</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>details.difference_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/21_monthly_budget/pattern.xlsx
+++ b/tests/fixtures/21_monthly_budget/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_income</t>
+          <t>col_proj_cost</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Income:</t>
+          <t>Projected Cost</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c_cat</t>
+          <t>col_actual_cost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Actual Cost</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c_proj</t>
+          <t>col_difference</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,19 +495,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Difference</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_act</t>
+          <t>budget.title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,29 +517,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_diff</t>
+          <t>income.proj_total</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>budget.income</t>
+          <t>income.actual_total</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item.category</t>
+          <t>balance.projected</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item.projected</t>
+          <t>balance.actual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item.actual</t>
+          <t>balance.difference</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item.difference</t>
+          <t>expense.category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -656,85 +656,211 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>expense.projected</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cell:C4</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>budget.income</t>
+          <t>expense.actual</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>table:*</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>expense.difference</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>c_cat</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>c_proj</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>c_act</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>c_diff</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cell:B2</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>item.category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>item.projected</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>item.actual</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>item.difference</t>
+          <t>budget.title</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>cell:J4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>balance.projected</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cell:E6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>income.proj_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cell:J6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>balance.actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cell:J8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balance.difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cell:E10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>income.actual_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>col_proj_cost</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>col_actual_cost</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>col_difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DATA:*</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>expense.category</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>expense.projected</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>expense.actual</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>expense.difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
